--- a/sample_data/5_BAD_Wrong_Sheet_And_Headers.xlsx
+++ b/sample_data/5_BAD_Wrong_Sheet_And_Headers.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unknown Vendor Co.</t>
+          <t>[TEST] Unknown Vendor Co.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -474,7 +474,7 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>No TIN Given Corp.</t>
+          <t>[TEST] No TIN Given Corp.</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -499,7 +499,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ghost ATC Supplier</t>
+          <t>[TEST] Ghost ATC Supplier</t>
         </is>
       </c>
       <c r="C4" t="n">
